--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>75.16</v>
+        <v>61.9</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T04:31:04.584472Z</t>
+          <t>2026-06-16T04:44:38.582896Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-15T04:32:19.739622Z</t>
+          <t>2026-06-16T04:45:40.487594Z</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.6</v>
+        <v>0.04</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.9</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1.55</v>
+        <v>0.84</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.46</v>
+        <v>1.23</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2.4</v>
+        <v>1.23</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.9</v>
+        <v>0.67</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>12.18</v>
+        <v>12.12</v>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:28</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3234,14 +3234,14 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_001_login_page_renders → PASSED in 1.22s</t>
+          <t>[Authentication &amp; Redirection] test_001_login_page_renders → PASSED in 0.59s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:28</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3251,14 +3251,14 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_002_login_title → PASSED in 0.06s</t>
+          <t>[Authentication &amp; Redirection] test_002_login_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:28</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3275,7 +3275,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:28</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3285,14 +3285,14 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_004_login_email_input_exists → PASSED in 0.03s</t>
+          <t>[Authentication &amp; Redirection] test_004_login_email_input_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:29</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_005_login_submit_btn_exists → PASSED in 0.04s</t>
+          <t>[Authentication &amp; Redirection] test_005_login_submit_btn_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:29</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3319,14 +3319,14 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_006_login_register_link_exists → PASSED in 0.03s</t>
+          <t>[Authentication &amp; Redirection] test_006_login_register_link_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:29</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3336,14 +3336,14 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_007_login_brand_mark → PASSED in 0.02s</t>
+          <t>[Authentication &amp; Redirection] test_007_login_brand_mark → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:29</t>
+          <t>2026-06-16 04:44:58</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3353,14 +3353,14 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_008_login_logo_container → PASSED in 0.03s</t>
+          <t>[Authentication &amp; Redirection] test_008_login_logo_container → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:30</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3370,14 +3370,14 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_009_login_invalid_email_displays_error → PASSED in 1.78s</t>
+          <t>[Authentication &amp; Redirection] test_009_login_invalid_email_displays_error → PASSED in 1.38s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:31</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3387,14 +3387,14 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_010_register_page_renders → PASSED in 0.14s</t>
+          <t>[Authentication &amp; Redirection] test_010_register_page_renders → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:31</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_011_register_title → PASSED in 0.6s</t>
+          <t>[Authentication &amp; Redirection] test_011_register_title → PASSED in 0.04s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:31</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3428,7 +3428,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:31</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3438,14 +3438,14 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_013_register_name_input_exists → PASSED in 0.03s</t>
+          <t>[Authentication &amp; Redirection] test_013_register_name_input_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:31</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3455,14 +3455,14 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_014_register_email_input_exists → PASSED in 0.03s</t>
+          <t>[Authentication &amp; Redirection] test_014_register_email_input_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:31</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3472,14 +3472,14 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_015_register_submit_btn_exists → PASSED in 0.03s</t>
+          <t>[Authentication &amp; Redirection] test_015_register_submit_btn_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:31</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3489,14 +3489,14 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_016_register_login_link_exists → PASSED in 0.04s</t>
+          <t>[Authentication &amp; Redirection] test_016_register_login_link_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:32</t>
+          <t>2026-06-16 04:45:00</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_017_register_duplicate_email_error → PASSED in 0.9s</t>
+          <t>[Authentication &amp; Redirection] test_017_register_duplicate_email_error → PASSED in 0.56s</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:34</t>
+          <t>2026-06-16 04:45:01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3523,14 +3523,14 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_018_register_success_flow → PASSED in 1.55s</t>
+          <t>[Authentication &amp; Redirection] test_018_register_success_flow → PASSED in 0.84s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:36</t>
+          <t>2026-06-16 04:45:02</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3540,14 +3540,14 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_019_login_as_admin_redirects_dashboard → PASSED in 2.46s</t>
+          <t>[Admin Command Center] test_019_login_as_admin_redirects_dashboard → PASSED in 1.23s</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:39</t>
+          <t>2026-06-16 04:45:04</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_020_login_as_user_redirects_portal → PASSED in 2.4s</t>
+          <t>[Authentication &amp; Redirection] test_020_login_as_user_redirects_portal → PASSED in 1.23s</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:39</t>
+          <t>2026-06-16 04:45:04</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3574,14 +3574,14 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_021_route_protection_dashboard_direct → PASSED in 0.66s</t>
+          <t>[Safe Route Planner] test_021_route_protection_dashboard_direct → PASSED in 0.58s</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:40</t>
+          <t>2026-06-16 04:45:05</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3591,14 +3591,14 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_022_route_protection_portal_direct → PASSED in 0.64s</t>
+          <t>[Safe Route Planner] test_022_route_protection_portal_direct → PASSED in 0.52s</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:41</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3608,14 +3608,14 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_023_portal_home_welcome_title → PASSED in 1.47s</t>
+          <t>[User Portal - Home &amp; SOS] test_023_portal_home_welcome_title → PASSED in 1.23s</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:41</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3625,14 +3625,14 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_024_portal_home_subtitle → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_024_portal_home_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:41</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_025_portal_home_sos_btn_renders → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_025_portal_home_sos_btn_renders → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_026_portal_home_sos_initial_text → PASSED in 0.04s</t>
+          <t>[User Portal - Home &amp; SOS] test_026_portal_home_sos_initial_text → PASSED in 0.06s</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3676,14 +3676,14 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_027_portal_home_contacts_card_renders → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_027_portal_home_contacts_card_renders → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3693,14 +3693,14 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_028_portal_home_contacts_card_has_count → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_028_portal_home_contacts_card_has_count → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3710,14 +3710,14 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_029_portal_home_how_sos_works_card → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_029_portal_home_how_sos_works_card → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_030_portal_home_how_sos_works_steps → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_030_portal_home_how_sos_works_steps → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3744,14 +3744,14 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_031_portal_home_quick_actions_title → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_031_portal_home_quick_actions_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3761,14 +3761,14 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_032_portal_home_quick_action_contacts_link → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_032_portal_home_quick_action_contacts_link → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_033_portal_home_quick_action_report_link → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_033_portal_home_quick_action_report_link → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:42</t>
+          <t>2026-06-16 04:45:06</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3795,14 +3795,14 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_034_portal_home_quick_action_route_link → PASSED in 0.05s</t>
+          <t>[User Portal - Home &amp; SOS] test_034_portal_home_quick_action_route_link → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:43</t>
+          <t>2026-06-16 04:45:07</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3812,14 +3812,14 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_035_portal_home_sos_trigger_flow → PASSED in 1.18s</t>
+          <t>[User Portal - Home &amp; SOS] test_035_portal_home_sos_trigger_flow → PASSED in 1.08s</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:43</t>
+          <t>2026-06-16 04:45:07</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3829,14 +3829,14 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_036_portal_home_sos_coords_displayed → PASSED in 0.04s</t>
+          <t>[User Portal - Home &amp; SOS] test_036_portal_home_sos_coords_displayed → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:43</t>
+          <t>2026-06-16 04:45:07</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3846,14 +3846,14 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_037_portal_home_sos_btn_changes_to_sent → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_037_portal_home_sos_btn_changes_to_sent → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:44</t>
+          <t>2026-06-16 04:45:08</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3863,14 +3863,14 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_038_portal_contacts_navigation → PASSED in 0.73s</t>
+          <t>[Trusted Contacts] test_038_portal_contacts_navigation → PASSED in 0.56s</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:44</t>
+          <t>2026-06-16 04:45:08</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3880,14 +3880,14 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_039_portal_contacts_subtitle → PASSED in 0.04s</t>
+          <t>[Trusted Contacts] test_039_portal_contacts_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:44</t>
+          <t>2026-06-16 04:45:08</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_040_portal_contacts_form_title → PASSED in 0.04s</t>
+          <t>[Trusted Contacts] test_040_portal_contacts_form_title → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:44</t>
+          <t>2026-06-16 04:45:08</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3914,14 +3914,14 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_041_portal_contacts_name_input_exists → PASSED in 0.03s</t>
+          <t>[Trusted Contacts] test_041_portal_contacts_name_input_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:44</t>
+          <t>2026-06-16 04:45:08</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3931,14 +3931,14 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_042_portal_contacts_phone_input_exists → PASSED in 0.04s</t>
+          <t>[Trusted Contacts] test_042_portal_contacts_phone_input_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:44</t>
+          <t>2026-06-16 04:45:08</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3948,14 +3948,14 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_043_portal_contacts_submit_btn_exists → PASSED in 0.03s</t>
+          <t>[Trusted Contacts] test_043_portal_contacts_submit_btn_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:45</t>
+          <t>2026-06-16 04:45:09</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3965,14 +3965,14 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_044_portal_contacts_add_contact_success → PASSED in 1.33s</t>
+          <t>[Trusted Contacts] test_044_portal_contacts_add_contact_success → PASSED in 1.16s</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:45</t>
+          <t>2026-06-16 04:45:09</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3982,14 +3982,14 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_045_portal_contacts_input_cleared_on_success → PASSED in 0.03s</t>
+          <t>[Trusted Contacts] test_045_portal_contacts_input_cleared_on_success → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:45</t>
+          <t>2026-06-16 04:45:09</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3999,14 +3999,14 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_046_portal_contacts_initials_calculated_correctly → PASSED in 0.05s</t>
+          <t>[Trusted Contacts] test_046_portal_contacts_initials_calculated_correctly → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:45</t>
+          <t>2026-06-16 04:45:09</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -4016,14 +4016,14 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_047_portal_contacts_phone_link_anchor → PASSED in 0.04s</t>
+          <t>[Trusted Contacts] test_047_portal_contacts_phone_link_anchor → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:46</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4033,14 +4033,14 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_048_portal_contacts_multiple_contacts_list → PASSED in 0.9s</t>
+          <t>[Trusted Contacts] test_048_portal_contacts_multiple_contacts_list → PASSED in 0.67s</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:46</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:46</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4074,7 +4074,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:46</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -4084,14 +4084,14 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_051_portal_contacts_phone_input_required_attrs → PASSED in 0.1s</t>
+          <t>[Trusted Contacts] test_051_portal_contacts_phone_input_required_attrs → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_052_portal_contacts_header_icons → PASSED in 0.03s</t>
+          <t>[Trusted Contacts] test_052_portal_contacts_header_icons → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -4118,14 +4118,14 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_053_portal_report_navigation → PASSED in 0.21s</t>
+          <t>[Report Incident] test_053_portal_report_navigation → PASSED in 0.13s</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4135,14 +4135,14 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_054_portal_report_subtitle → PASSED in 0.02s</t>
+          <t>[Report Incident] test_054_portal_report_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4159,7 +4159,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4169,14 +4169,14 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_056_portal_report_incident_type_options → PASSED in 0.04s</t>
+          <t>[Report Incident] test_056_portal_report_incident_type_options → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4193,7 +4193,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4203,14 +4203,14 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_058_portal_report_description_field → PASSED in 0.02s</t>
+          <t>[Report Incident] test_058_portal_report_description_field → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4220,14 +4220,14 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_059_portal_report_use_mylocation_btn → PASSED in 0.02s</t>
+          <t>[Report Incident] test_059_portal_report_use_mylocation_btn → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4237,14 +4237,14 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_060_portal_report_location_coordinates_text_initial → PASSED in 0.03s</t>
+          <t>[Report Incident] test_060_portal_report_location_coordinates_text_initial → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:47</t>
+          <t>2026-06-16 04:45:10</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4254,14 +4254,14 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_061_portal_report_google_map_present → PASSED in 0.02s</t>
+          <t>[Report Incident] test_061_portal_report_google_map_present → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:48</t>
+          <t>2026-06-16 04:45:11</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4271,14 +4271,14 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_062_portal_report_click_use_mylocation → PASSED in 1.14s</t>
+          <t>[Report Incident] test_062_portal_report_click_use_mylocation → PASSED in 1.07s</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:50</t>
+          <t>2026-06-16 04:45:12</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4288,14 +4288,14 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_063_portal_report_submit_success_flow → PASSED in 1.45s</t>
+          <t>[Report Incident] test_063_portal_report_submit_success_flow → PASSED in 1.26s</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:50</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4305,14 +4305,14 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_064_portal_report_reset_form_flow → PASSED in 0.21s</t>
+          <t>[Report Incident] test_064_portal_report_reset_form_flow → PASSED in 0.06s</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:50</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4322,14 +4322,14 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_065_portal_report_map_instructions_text → PASSED in 0.03s</t>
+          <t>[Report Incident] test_065_portal_report_map_instructions_text → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:50</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4339,14 +4339,14 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_066_portal_route_navigation → PASSED in 0.75s</t>
+          <t>[Safe Route Planner] test_066_portal_route_navigation → PASSED in 0.59s</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:51</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4356,14 +4356,14 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_067_portal_route_subtitle → PASSED in 0.03s</t>
+          <t>[Safe Route Planner] test_067_portal_route_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:51</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4373,14 +4373,14 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_068_portal_route_from_input_exists → PASSED in 0.03s</t>
+          <t>[Safe Route Planner] test_068_portal_route_from_input_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:51</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4390,14 +4390,14 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_069_portal_route_to_input_exists → PASSED in 0.04s</t>
+          <t>[Safe Route Planner] test_069_portal_route_to_input_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:51</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4407,14 +4407,14 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_070_portal_route_use_mylocation_btn → PASSED in 0.02s</t>
+          <t>[Safe Route Planner] test_070_portal_route_use_mylocation_btn → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:51</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4424,14 +4424,14 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_071_portal_route_find_route_btn → PASSED in 0.03s</t>
+          <t>[Safe Route Planner] test_071_portal_route_find_route_btn → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:51</t>
+          <t>2026-06-16 04:45:13</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4441,14 +4441,14 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_072_portal_route_map_container_exists → PASSED in 0.04s</t>
+          <t>[Safe Route Planner] test_072_portal_route_map_container_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:52</t>
+          <t>2026-06-16 04:45:14</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4458,14 +4458,14 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_073_portal_route_click_use_mylocation_fills_origin → PASSED in 1.14s</t>
+          <t>[Safe Route Planner] test_073_portal_route_click_use_mylocation_fills_origin → PASSED in 1.07s</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:55</t>
+          <t>2026-06-16 04:45:17</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4475,14 +4475,14 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_074_portal_route_empty_inputs_error_not_triggered_initially → PASSED in 3.03s</t>
+          <t>[Safe Route Planner] test_074_portal_route_empty_inputs_error_not_triggered_initially → PASSED in 3.02s</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:57</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4492,14 +4492,14 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_075_portal_route_find_route_mock_submit → PASSED in 2.48s</t>
+          <t>[Safe Route Planner] test_075_portal_route_find_route_mock_submit → PASSED in 2.18s</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4509,14 +4509,14 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_076_portal_profile_navigation → PASSED in 0.73s</t>
+          <t>[User Profile] test_076_portal_profile_navigation → PASSED in 0.57s</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4526,14 +4526,14 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_077_portal_profile_subtitle → PASSED in 0.04s</t>
+          <t>[User Profile] test_077_portal_profile_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4543,14 +4543,14 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_078_portal_profile_initials_circle → PASSED in 0.03s</t>
+          <t>[User Profile] test_078_portal_profile_initials_circle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4567,7 +4567,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4584,7 +4584,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4601,7 +4601,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4618,7 +4618,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4662,14 +4662,14 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_085_portal_profile_details_rows → PASSED in 0.04s</t>
+          <t>[User Profile] test_085_portal_profile_details_rows → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:31:58</t>
+          <t>2026-06-16 04:45:20</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4679,14 +4679,14 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_086_portal_profile_logout_btn_exists → PASSED in 0.04s</t>
+          <t>[User Profile] test_086_portal_profile_logout_btn_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_087_admin_dashboard_navigation → PASSED in 2.88s</t>
+          <t>[Admin Command Center] test_087_admin_dashboard_navigation → PASSED in 2.74s</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4713,14 +4713,14 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_088_admin_dashboard_title → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_088_admin_dashboard_title → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4730,14 +4730,14 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_089_admin_dashboard_subtitle → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_089_admin_dashboard_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4747,14 +4747,14 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_090_admin_dashboard_live_sos_alert_appears → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_090_admin_dashboard_live_sos_alert_appears → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4764,14 +4764,14 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_091_admin_dashboard_live_sos_banner_details → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_091_admin_dashboard_live_sos_banner_details → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4781,14 +4781,14 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_092_admin_dashboard_live_sos_resolve_btn_exists → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_092_admin_dashboard_live_sos_resolve_btn_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4798,14 +4798,14 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_093_admin_dashboard_stat_card_total_users → PASSED in 0.04s</t>
+          <t>[Admin Command Center] test_093_admin_dashboard_stat_card_total_users → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:01</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4815,14 +4815,14 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_094_admin_dashboard_stat_card_total_reports → PASSED in 0.03s</t>
+          <t>[Report Incident] test_094_admin_dashboard_stat_card_total_reports → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4832,14 +4832,14 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_095_admin_dashboard_stat_card_active_emergencies → PASSED in 0.03s</t>
+          <t>[Admin Command Center] test_095_admin_dashboard_stat_card_active_emergencies → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4856,7 +4856,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4866,14 +4866,14 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_097_admin_dashboard_hotspots_title → PASSED in 0.04s</t>
+          <t>[Admin Command Center] test_097_admin_dashboard_hotspots_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_098_admin_dashboard_hotspots_grid_renders → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_098_admin_dashboard_hotspots_grid_renders → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4900,14 +4900,14 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_099_admin_dashboard_live_map_title → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_099_admin_dashboard_live_map_title → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_100_admin_dashboard_heatmap_title → PASSED in 0.03s</t>
+          <t>[Admin Command Center] test_100_admin_dashboard_heatmap_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4934,14 +4934,14 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_101_admin_dashboard_reports_table_title → PASSED in 0.04s</t>
+          <t>[Report Incident] test_101_admin_dashboard_reports_table_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4951,14 +4951,14 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_102_admin_dashboard_reports_table_headers → PASSED in 0.15s</t>
+          <t>[Report Incident] test_102_admin_dashboard_reports_table_headers → PASSED in 0.07s</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4968,14 +4968,14 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_103_admin_dashboard_reports_table_row_data → PASSED in 0.03s</t>
+          <t>[Report Incident] test_103_admin_dashboard_reports_table_row_data → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_104_admin_dashboard_users_table_title → PASSED in 0.03s</t>
+          <t>[Admin Command Center] test_104_admin_dashboard_users_table_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -5002,14 +5002,14 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_105_admin_dashboard_users_table_data → PASSED in 0.07s</t>
+          <t>[Admin Command Center] test_105_admin_dashboard_users_table_data → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5019,14 +5019,14 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_106_admin_dashboard_live_emergencies_section → PASSED in 0.03s</t>
+          <t>[Admin Command Center] test_106_admin_dashboard_live_emergencies_section → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:02</t>
+          <t>2026-06-16 04:45:23</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5036,14 +5036,14 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_107_admin_dashboard_live_emergencies_cards → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_107_admin_dashboard_live_emergencies_cards → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:03</t>
+          <t>2026-06-16 04:45:25</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_108_admin_dashboard_emergency_modal_details_flow → PASSED in 1.29s</t>
+          <t>[Admin Command Center] test_108_admin_dashboard_emergency_modal_details_flow → PASSED in 1.16s</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:16</t>
+          <t>2026-06-16 04:45:37</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5070,14 +5070,14 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_109_admin_dashboard_resolve_sos_flow → PASSED in 12.18s</t>
+          <t>[User Portal - Home &amp; SOS] test_109_admin_dashboard_resolve_sos_flow → PASSED in 12.12s</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 04:32:17</t>
+          <t>2026-06-16 04:45:38</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_110_admin_logout_redirection → PASSED in 1.11s</t>
+          <t>[Admin Command Center] test_110_admin_logout_redirection → PASSED in 1.07s</t>
         </is>
       </c>
     </row>

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>61.9</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T04:44:38.582896Z</t>
+          <t>2026-06-16T06:03:24.633901Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T04:45:40.487594Z</t>
+          <t>2026-06-16T06:04:29.286234Z</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.84</v>
+        <v>0.75</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.02</v>
+        <v>0.42</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.02</v>
+        <v>0.42</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.02</v>
+        <v>0.75</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>12.12</v>
+        <v>12.18</v>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
@@ -3123,9 +3123,32 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Authentication &amp; Redirection</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>test_111_pages_deployment_check</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
@@ -3196,7 +3219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3224,7 +3247,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:43</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3234,14 +3257,14 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_001_login_page_renders → PASSED in 0.59s</t>
+          <t>[Authentication &amp; Redirection] test_001_login_page_renders → PASSED in 0.5s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:43</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3258,7 +3281,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:43</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3275,7 +3298,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:43</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3285,14 +3308,14 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_004_login_email_input_exists → PASSED in 0.01s</t>
+          <t>[Authentication &amp; Redirection] test_004_login_email_input_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:43</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3309,7 +3332,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:43</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3326,7 +3349,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:43</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3343,7 +3366,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:44:58</t>
+          <t>2026-06-16 06:03:44</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3360,7 +3383,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3370,14 +3393,14 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_009_login_invalid_email_displays_error → PASSED in 1.38s</t>
+          <t>[Authentication &amp; Redirection] test_009_login_invalid_email_displays_error → PASSED in 1.29s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3394,7 +3417,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3404,14 +3427,14 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_011_register_title → PASSED in 0.04s</t>
+          <t>[Authentication &amp; Redirection] test_011_register_title → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3421,14 +3444,14 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_012_register_subtitle → PASSED in 0.03s</t>
+          <t>[Authentication &amp; Redirection] test_012_register_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3445,7 +3468,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3462,7 +3485,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3479,7 +3502,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:45</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3496,7 +3519,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:00</t>
+          <t>2026-06-16 06:03:46</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3506,14 +3529,14 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_017_register_duplicate_email_error → PASSED in 0.56s</t>
+          <t>[Authentication &amp; Redirection] test_017_register_duplicate_email_error → PASSED in 0.59s</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:01</t>
+          <t>2026-06-16 06:03:46</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3523,14 +3546,14 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_018_register_success_flow → PASSED in 0.84s</t>
+          <t>[Authentication &amp; Redirection] test_018_register_success_flow → PASSED in 0.75s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:02</t>
+          <t>2026-06-16 06:03:47</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3540,14 +3563,14 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_019_login_as_admin_redirects_dashboard → PASSED in 1.23s</t>
+          <t>[Admin Command Center] test_019_login_as_admin_redirects_dashboard → PASSED in 1.22s</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:04</t>
+          <t>2026-06-16 06:03:49</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3557,14 +3580,14 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_020_login_as_user_redirects_portal → PASSED in 1.23s</t>
+          <t>[Authentication &amp; Redirection] test_020_login_as_user_redirects_portal → PASSED in 1.22s</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:04</t>
+          <t>2026-06-16 06:03:49</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3581,7 +3604,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:05</t>
+          <t>2026-06-16 06:03:50</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3598,7 +3621,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:51</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3608,14 +3631,14 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_023_portal_home_welcome_title → PASSED in 1.23s</t>
+          <t>[User Portal - Home &amp; SOS] test_023_portal_home_welcome_title → PASSED in 1.65s</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:52</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3625,14 +3648,14 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_024_portal_home_subtitle → PASSED in 0.01s</t>
+          <t>[User Portal - Home &amp; SOS] test_024_portal_home_subtitle → PASSED in 0.36s</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:52</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3642,14 +3665,14 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_025_portal_home_sos_btn_renders → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_025_portal_home_sos_btn_renders → PASSED in 0.42s</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:52</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3659,14 +3682,14 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_026_portal_home_sos_initial_text → PASSED in 0.06s</t>
+          <t>[User Portal - Home &amp; SOS] test_026_portal_home_sos_initial_text → PASSED in 0.11s</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:52</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3676,14 +3699,14 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_027_portal_home_contacts_card_renders → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_027_portal_home_contacts_card_renders → PASSED in 0.04s</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:52</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3693,14 +3716,14 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_028_portal_home_contacts_card_has_count → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_028_portal_home_contacts_card_has_count → PASSED in 0.04s</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:52</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3710,14 +3733,14 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_029_portal_home_how_sos_works_card → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_029_portal_home_how_sos_works_card → PASSED in 0.05s</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:52</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3727,14 +3750,14 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_030_portal_home_how_sos_works_steps → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_030_portal_home_how_sos_works_steps → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:53</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3744,14 +3767,14 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_031_portal_home_quick_actions_title → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_031_portal_home_quick_actions_title → PASSED in 0.42s</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:54</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3761,14 +3784,14 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_032_portal_home_quick_action_contacts_link → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_032_portal_home_quick_action_contacts_link → PASSED in 0.75s</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:54</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3778,14 +3801,14 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_033_portal_home_quick_action_report_link → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_033_portal_home_quick_action_report_link → PASSED in 0.13s</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:06</t>
+          <t>2026-06-16 06:03:54</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3795,14 +3818,14 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_034_portal_home_quick_action_route_link → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_034_portal_home_quick_action_route_link → PASSED in 0.07s</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:07</t>
+          <t>2026-06-16 06:03:55</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3812,14 +3835,14 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_035_portal_home_sos_trigger_flow → PASSED in 1.08s</t>
+          <t>[User Portal - Home &amp; SOS] test_035_portal_home_sos_trigger_flow → PASSED in 1.27s</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:07</t>
+          <t>2026-06-16 06:03:55</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3829,14 +3852,14 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_036_portal_home_sos_coords_displayed → PASSED in 0.01s</t>
+          <t>[User Portal - Home &amp; SOS] test_036_portal_home_sos_coords_displayed → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:07</t>
+          <t>2026-06-16 06:03:55</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3846,14 +3869,14 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_037_portal_home_sos_btn_changes_to_sent → PASSED in 0.01s</t>
+          <t>[User Portal - Home &amp; SOS] test_037_portal_home_sos_btn_changes_to_sent → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:08</t>
+          <t>2026-06-16 06:03:56</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3863,14 +3886,14 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_038_portal_contacts_navigation → PASSED in 0.56s</t>
+          <t>[Trusted Contacts] test_038_portal_contacts_navigation → PASSED in 0.61s</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:08</t>
+          <t>2026-06-16 06:03:56</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3880,14 +3903,14 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_039_portal_contacts_subtitle → PASSED in 0.01s</t>
+          <t>[Trusted Contacts] test_039_portal_contacts_subtitle → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:08</t>
+          <t>2026-06-16 06:03:56</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3897,14 +3920,14 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_040_portal_contacts_form_title → PASSED in 0.01s</t>
+          <t>[Trusted Contacts] test_040_portal_contacts_form_title → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:08</t>
+          <t>2026-06-16 06:03:56</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3914,14 +3937,14 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_041_portal_contacts_name_input_exists → PASSED in 0.01s</t>
+          <t>[Trusted Contacts] test_041_portal_contacts_name_input_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:08</t>
+          <t>2026-06-16 06:03:56</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3931,14 +3954,14 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_042_portal_contacts_phone_input_exists → PASSED in 0.01s</t>
+          <t>[Trusted Contacts] test_042_portal_contacts_phone_input_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:08</t>
+          <t>2026-06-16 06:03:56</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3948,14 +3971,14 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_043_portal_contacts_submit_btn_exists → PASSED in 0.01s</t>
+          <t>[Trusted Contacts] test_043_portal_contacts_submit_btn_exists → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:09</t>
+          <t>2026-06-16 06:03:57</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3965,14 +3988,14 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_044_portal_contacts_add_contact_success → PASSED in 1.16s</t>
+          <t>[Trusted Contacts] test_044_portal_contacts_add_contact_success → PASSED in 1.25s</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:09</t>
+          <t>2026-06-16 06:03:57</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3982,14 +4005,14 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_045_portal_contacts_input_cleared_on_success → PASSED in 0.01s</t>
+          <t>[Trusted Contacts] test_045_portal_contacts_input_cleared_on_success → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:09</t>
+          <t>2026-06-16 06:03:57</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3999,14 +4022,14 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_046_portal_contacts_initials_calculated_correctly → PASSED in 0.01s</t>
+          <t>[Trusted Contacts] test_046_portal_contacts_initials_calculated_correctly → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:09</t>
+          <t>2026-06-16 06:03:57</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -4023,7 +4046,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:58</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4033,14 +4056,14 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_048_portal_contacts_multiple_contacts_list → PASSED in 0.67s</t>
+          <t>[Trusted Contacts] test_048_portal_contacts_multiple_contacts_list → PASSED in 0.7s</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:58</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -4050,14 +4073,14 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_049_portal_contacts_layout_columns → PASSED in 0.02s</t>
+          <t>[Trusted Contacts] test_049_portal_contacts_layout_columns → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:58</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4074,7 +4097,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:58</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -4091,7 +4114,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:58</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4108,7 +4131,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -4118,14 +4141,14 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_053_portal_report_navigation → PASSED in 0.13s</t>
+          <t>[Report Incident] test_053_portal_report_navigation → PASSED in 0.57s</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4142,7 +4165,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4159,7 +4182,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4169,14 +4192,14 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_056_portal_report_incident_type_options → PASSED in 0.02s</t>
+          <t>[Report Incident] test_056_portal_report_incident_type_options → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4186,14 +4209,14 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_057_portal_report_severity_buttons → PASSED in 0.01s</t>
+          <t>[Report Incident] test_057_portal_report_severity_buttons → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4203,14 +4226,14 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_058_portal_report_description_field → PASSED in 0.01s</t>
+          <t>[Report Incident] test_058_portal_report_description_field → PASSED in 0.05s</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4227,7 +4250,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4237,14 +4260,14 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_060_portal_report_location_coordinates_text_initial → PASSED in 0.02s</t>
+          <t>[Report Incident] test_060_portal_report_location_coordinates_text_initial → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:10</t>
+          <t>2026-06-16 06:03:59</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4254,14 +4277,14 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_061_portal_report_google_map_present → PASSED in 0.03s</t>
+          <t>[Report Incident] test_061_portal_report_google_map_present → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:11</t>
+          <t>2026-06-16 06:04:00</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4271,14 +4294,14 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_062_portal_report_click_use_mylocation → PASSED in 1.07s</t>
+          <t>[Report Incident] test_062_portal_report_click_use_mylocation → PASSED in 1.09s</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:12</t>
+          <t>2026-06-16 06:04:01</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4288,14 +4311,14 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_063_portal_report_submit_success_flow → PASSED in 1.26s</t>
+          <t>[Report Incident] test_063_portal_report_submit_success_flow → PASSED in 1.25s</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:01</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4305,14 +4328,14 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_064_portal_report_reset_form_flow → PASSED in 0.06s</t>
+          <t>[Report Incident] test_064_portal_report_reset_form_flow → PASSED in 0.18s</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:01</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4329,7 +4352,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:02</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4339,14 +4362,14 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_066_portal_route_navigation → PASSED in 0.59s</t>
+          <t>[Safe Route Planner] test_066_portal_route_navigation → PASSED in 0.58s</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:02</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4363,7 +4386,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:02</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4373,14 +4396,14 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_068_portal_route_from_input_exists → PASSED in 0.02s</t>
+          <t>[Safe Route Planner] test_068_portal_route_from_input_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:02</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4390,14 +4413,14 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_069_portal_route_to_input_exists → PASSED in 0.02s</t>
+          <t>[Safe Route Planner] test_069_portal_route_to_input_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:02</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4414,7 +4437,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:02</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4431,7 +4454,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:13</t>
+          <t>2026-06-16 06:04:02</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4448,7 +4471,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:14</t>
+          <t>2026-06-16 06:04:03</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4465,7 +4488,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:17</t>
+          <t>2026-06-16 06:04:06</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4482,7 +4505,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:08</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4492,14 +4515,14 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_075_portal_route_find_route_mock_submit → PASSED in 2.18s</t>
+          <t>[Safe Route Planner] test_075_portal_route_find_route_mock_submit → PASSED in 2.17s</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4509,14 +4532,14 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_076_portal_profile_navigation → PASSED in 0.57s</t>
+          <t>[User Profile] test_076_portal_profile_navigation → PASSED in 0.56s</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4533,7 +4556,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4543,14 +4566,14 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_078_portal_profile_initials_circle → PASSED in 0.01s</t>
+          <t>[User Profile] test_078_portal_profile_initials_circle → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4567,7 +4590,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4577,14 +4600,14 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_080_portal_profile_email → PASSED in 0.02s</t>
+          <t>[User Profile] test_080_portal_profile_email → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4594,14 +4617,14 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_081_portal_profile_role_chip → PASSED in 0.02s</t>
+          <t>[User Profile] test_081_portal_profile_role_chip → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4618,7 +4641,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4635,7 +4658,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4652,7 +4675,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4669,7 +4692,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:20</t>
+          <t>2026-06-16 06:04:09</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4679,14 +4702,14 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_086_portal_profile_logout_btn_exists → PASSED in 0.01s</t>
+          <t>[User Profile] test_086_portal_profile_logout_btn_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4703,7 +4726,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4713,14 +4736,14 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_088_admin_dashboard_title → PASSED in 0.01s</t>
+          <t>[Admin Command Center] test_088_admin_dashboard_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4730,14 +4753,14 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_089_admin_dashboard_subtitle → PASSED in 0.01s</t>
+          <t>[Admin Command Center] test_089_admin_dashboard_subtitle → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4754,7 +4777,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4764,14 +4787,14 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_091_admin_dashboard_live_sos_banner_details → PASSED in 0.01s</t>
+          <t>[User Portal - Home &amp; SOS] test_091_admin_dashboard_live_sos_banner_details → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4788,7 +4811,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4805,7 +4828,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4822,7 +4845,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4839,7 +4862,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4856,7 +4879,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4873,7 +4896,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4890,7 +4913,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4907,7 +4930,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4917,14 +4940,14 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_100_admin_dashboard_heatmap_title → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_100_admin_dashboard_heatmap_title → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4941,7 +4964,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4958,7 +4981,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4975,7 +4998,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4992,7 +5015,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -5009,7 +5032,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5026,7 +5049,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:23</t>
+          <t>2026-06-16 06:04:12</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5043,7 +5066,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:25</t>
+          <t>2026-06-16 06:04:13</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -5053,14 +5076,14 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_108_admin_dashboard_emergency_modal_details_flow → PASSED in 1.16s</t>
+          <t>[Admin Command Center] test_108_admin_dashboard_emergency_modal_details_flow → PASSED in 1.15s</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:37</t>
+          <t>2026-06-16 06:04:25</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5070,14 +5093,14 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_109_admin_dashboard_resolve_sos_flow → PASSED in 12.12s</t>
+          <t>[User Portal - Home &amp; SOS] test_109_admin_dashboard_resolve_sos_flow → PASSED in 12.18s</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 04:45:38</t>
+          <t>2026-06-16 06:04:27</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5087,7 +5110,24 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_110_admin_logout_redirection → PASSED in 1.07s</t>
+          <t>[Admin Command Center] test_110_admin_logout_redirection → PASSED in 1.08s</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16 06:04:27</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>[Authentication &amp; Redirection] test_111_pages_deployment_check → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7889,6 +7929,31 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Authentication &amp; Redirection</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>test_111_pages_deployment_check</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>None — test passed successfully.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>64.65000000000001</v>
+        <v>49.83</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T06:03:24.633901Z</t>
+          <t>2026-06-16T06:20:14.937875Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-16T06:04:29.286234Z</t>
+          <t>2026-06-16T06:21:04.769658Z</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.36</v>
+        <v>0.02</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.42</v>
+        <v>0.02</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.42</v>
+        <v>0.02</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.75</v>
+        <v>0.03</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.13</v>
+        <v>0.02</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.57</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>12.18</v>
+        <v>12.15</v>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:43</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -3257,14 +3257,14 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_001_login_page_renders → PASSED in 0.5s</t>
+          <t>[Authentication &amp; Redirection] test_001_login_page_renders → PASSED in 0.52s</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:43</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3281,7 +3281,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:43</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3291,14 +3291,14 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_003_login_subtitle → PASSED in 0.02s</t>
+          <t>[Authentication &amp; Redirection] test_003_login_subtitle → PASSED in 0.12s</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:43</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3308,14 +3308,14 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_004_login_email_input_exists → PASSED in 0.02s</t>
+          <t>[Authentication &amp; Redirection] test_004_login_email_input_exists → PASSED in 0.06s</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:43</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -3325,14 +3325,14 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_005_login_submit_btn_exists → PASSED in 0.01s</t>
+          <t>[Authentication &amp; Redirection] test_005_login_submit_btn_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:43</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:43</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:44</t>
+          <t>2026-06-16 06:20:23</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3393,14 +3393,14 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_009_login_invalid_email_displays_error → PASSED in 1.29s</t>
+          <t>[Authentication &amp; Redirection] test_009_login_invalid_email_displays_error → PASSED in 1.3s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3410,14 +3410,14 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_010_register_page_renders → PASSED in 0.02s</t>
+          <t>[Authentication &amp; Redirection] test_010_register_page_renders → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3434,7 +3434,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3451,7 +3451,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3468,7 +3468,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3485,7 +3485,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3502,7 +3502,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:45</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3512,14 +3512,14 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_016_register_login_link_exists → PASSED in 0.01s</t>
+          <t>[Authentication &amp; Redirection] test_016_register_login_link_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:46</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3529,14 +3529,14 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_017_register_duplicate_email_error → PASSED in 0.59s</t>
+          <t>[Authentication &amp; Redirection] test_017_register_duplicate_email_error → PASSED in 0.27s</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:46</t>
+          <t>2026-06-16 06:20:25</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -3546,14 +3546,14 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_018_register_success_flow → PASSED in 0.75s</t>
+          <t>[Authentication &amp; Redirection] test_018_register_success_flow → PASSED in 0.4s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:47</t>
+          <t>2026-06-16 06:20:27</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -3563,14 +3563,14 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_019_login_as_admin_redirects_dashboard → PASSED in 1.22s</t>
+          <t>[Admin Command Center] test_019_login_as_admin_redirects_dashboard → PASSED in 1.24s</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:49</t>
+          <t>2026-06-16 06:20:28</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -3580,14 +3580,14 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>[Authentication &amp; Redirection] test_020_login_as_user_redirects_portal → PASSED in 1.22s</t>
+          <t>[Authentication &amp; Redirection] test_020_login_as_user_redirects_portal → PASSED in 1.28s</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:49</t>
+          <t>2026-06-16 06:20:29</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -3597,14 +3597,14 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_021_route_protection_dashboard_direct → PASSED in 0.58s</t>
+          <t>[Safe Route Planner] test_021_route_protection_dashboard_direct → PASSED in 0.59s</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:50</t>
+          <t>2026-06-16 06:20:29</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3621,7 +3621,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:51</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_023_portal_home_welcome_title → PASSED in 1.65s</t>
+          <t>[User Portal - Home &amp; SOS] test_023_portal_home_welcome_title → PASSED in 1.23s</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:52</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -3648,14 +3648,14 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_024_portal_home_subtitle → PASSED in 0.36s</t>
+          <t>[User Portal - Home &amp; SOS] test_024_portal_home_subtitle → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:52</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -3665,14 +3665,14 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_025_portal_home_sos_btn_renders → PASSED in 0.42s</t>
+          <t>[User Portal - Home &amp; SOS] test_025_portal_home_sos_btn_renders → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:52</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -3682,14 +3682,14 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_026_portal_home_sos_initial_text → PASSED in 0.11s</t>
+          <t>[User Portal - Home &amp; SOS] test_026_portal_home_sos_initial_text → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:52</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3699,14 +3699,14 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_027_portal_home_contacts_card_renders → PASSED in 0.04s</t>
+          <t>[User Portal - Home &amp; SOS] test_027_portal_home_contacts_card_renders → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:52</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_028_portal_home_contacts_card_has_count → PASSED in 0.04s</t>
+          <t>[User Portal - Home &amp; SOS] test_028_portal_home_contacts_card_has_count → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:52</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_029_portal_home_how_sos_works_card → PASSED in 0.05s</t>
+          <t>[User Portal - Home &amp; SOS] test_029_portal_home_how_sos_works_card → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:52</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -3750,14 +3750,14 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_030_portal_home_how_sos_works_steps → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_030_portal_home_how_sos_works_steps → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:53</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3767,14 +3767,14 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_031_portal_home_quick_actions_title → PASSED in 0.42s</t>
+          <t>[User Portal - Home &amp; SOS] test_031_portal_home_quick_actions_title → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:54</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3784,14 +3784,14 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_032_portal_home_quick_action_contacts_link → PASSED in 0.75s</t>
+          <t>[User Portal - Home &amp; SOS] test_032_portal_home_quick_action_contacts_link → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:54</t>
+          <t>2026-06-16 06:20:30</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_033_portal_home_quick_action_report_link → PASSED in 0.13s</t>
+          <t>[User Portal - Home &amp; SOS] test_033_portal_home_quick_action_report_link → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:54</t>
+          <t>2026-06-16 06:20:31</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3818,14 +3818,14 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_034_portal_home_quick_action_route_link → PASSED in 0.07s</t>
+          <t>[User Portal - Home &amp; SOS] test_034_portal_home_quick_action_route_link → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:55</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -3835,14 +3835,14 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_035_portal_home_sos_trigger_flow → PASSED in 1.27s</t>
+          <t>[User Portal - Home &amp; SOS] test_035_portal_home_sos_trigger_flow → PASSED in 1.09s</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:55</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3852,14 +3852,14 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_036_portal_home_sos_coords_displayed → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_036_portal_home_sos_coords_displayed → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:55</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_037_portal_home_sos_btn_changes_to_sent → PASSED in 0.03s</t>
+          <t>[User Portal - Home &amp; SOS] test_037_portal_home_sos_btn_changes_to_sent → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:56</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3886,14 +3886,14 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_038_portal_contacts_navigation → PASSED in 0.61s</t>
+          <t>[Trusted Contacts] test_038_portal_contacts_navigation → PASSED in 0.56s</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:56</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_039_portal_contacts_subtitle → PASSED in 0.02s</t>
+          <t>[Trusted Contacts] test_039_portal_contacts_subtitle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:56</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3920,14 +3920,14 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_040_portal_contacts_form_title → PASSED in 0.03s</t>
+          <t>[Trusted Contacts] test_040_portal_contacts_form_title → PASSED in 0.04s</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:56</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:56</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:56</t>
+          <t>2026-06-16 06:20:32</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3971,14 +3971,14 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_043_portal_contacts_submit_btn_exists → PASSED in 0.03s</t>
+          <t>[Trusted Contacts] test_043_portal_contacts_submit_btn_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:57</t>
+          <t>2026-06-16 06:20:33</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3988,14 +3988,14 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_044_portal_contacts_add_contact_success → PASSED in 1.25s</t>
+          <t>[Trusted Contacts] test_044_portal_contacts_add_contact_success → PASSED in 1.17s</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:57</t>
+          <t>2026-06-16 06:20:33</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -4005,14 +4005,14 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_045_portal_contacts_input_cleared_on_success → PASSED in 0.02s</t>
+          <t>[Trusted Contacts] test_045_portal_contacts_input_cleared_on_success → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:57</t>
+          <t>2026-06-16 06:20:33</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -4022,14 +4022,14 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_046_portal_contacts_initials_calculated_correctly → PASSED in 0.02s</t>
+          <t>[Trusted Contacts] test_046_portal_contacts_initials_calculated_correctly → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:57</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -4046,7 +4046,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:58</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_048_portal_contacts_multiple_contacts_list → PASSED in 0.7s</t>
+          <t>[Trusted Contacts] test_048_portal_contacts_multiple_contacts_list → PASSED in 0.67s</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:58</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -4080,7 +4080,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:58</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -4097,7 +4097,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:58</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:58</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_053_portal_report_navigation → PASSED in 0.57s</t>
+          <t>[Report Incident] test_053_portal_report_navigation → PASSED in 0.07s</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4165,7 +4165,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -4199,7 +4199,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4209,14 +4209,14 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_057_portal_report_severity_buttons → PASSED in 0.03s</t>
+          <t>[Report Incident] test_057_portal_report_severity_buttons → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4226,14 +4226,14 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_058_portal_report_description_field → PASSED in 0.05s</t>
+          <t>[Report Incident] test_058_portal_report_description_field → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_059_portal_report_use_mylocation_btn → PASSED in 0.01s</t>
+          <t>[Report Incident] test_059_portal_report_use_mylocation_btn → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4260,14 +4260,14 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_060_portal_report_location_coordinates_text_initial → PASSED in 0.01s</t>
+          <t>[Report Incident] test_060_portal_report_location_coordinates_text_initial → PASSED in 0.03s</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:03:59</t>
+          <t>2026-06-16 06:20:34</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4284,7 +4284,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:00</t>
+          <t>2026-06-16 06:20:36</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_062_portal_report_click_use_mylocation → PASSED in 1.09s</t>
+          <t>[Report Incident] test_062_portal_report_click_use_mylocation → PASSED in 1.08s</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:01</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_063_portal_report_submit_success_flow → PASSED in 1.25s</t>
+          <t>[Report Incident] test_063_portal_report_submit_success_flow → PASSED in 1.21s</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:01</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_064_portal_report_reset_form_flow → PASSED in 0.18s</t>
+          <t>[Report Incident] test_064_portal_report_reset_form_flow → PASSED in 0.06s</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:01</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -4352,7 +4352,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:02</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4362,14 +4362,14 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_066_portal_route_navigation → PASSED in 0.58s</t>
+          <t>[Safe Route Planner] test_066_portal_route_navigation → PASSED in 0.56s</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:02</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4386,7 +4386,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:02</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:02</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_069_portal_route_to_input_exists → PASSED in 0.01s</t>
+          <t>[Safe Route Planner] test_069_portal_route_to_input_exists → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:02</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:02</t>
+          <t>2026-06-16 06:20:37</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:02</t>
+          <t>2026-06-16 06:20:38</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -4464,14 +4464,14 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_072_portal_route_map_container_exists → PASSED in 0.02s</t>
+          <t>[Safe Route Planner] test_072_portal_route_map_container_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:03</t>
+          <t>2026-06-16 06:20:39</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_073_portal_route_click_use_mylocation_fills_origin → PASSED in 1.07s</t>
+          <t>[Safe Route Planner] test_073_portal_route_click_use_mylocation_fills_origin → PASSED in 1.06s</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:06</t>
+          <t>2026-06-16 06:20:42</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>[Safe Route Planner] test_074_portal_route_empty_inputs_error_not_triggered_initially → PASSED in 3.02s</t>
+          <t>[Safe Route Planner] test_074_portal_route_empty_inputs_error_not_triggered_initially → PASSED in 3.06s</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:08</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4522,7 +4522,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4556,7 +4556,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4566,14 +4566,14 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_078_portal_profile_initials_circle → PASSED in 0.02s</t>
+          <t>[User Profile] test_078_portal_profile_initials_circle → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4583,14 +4583,14 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_079_portal_profile_display_name → PASSED in 0.02s</t>
+          <t>[User Profile] test_079_portal_profile_display_name → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4634,14 +4634,14 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_082_portal_profile_stats_contacts_count → PASSED in 0.02s</t>
+          <t>[Trusted Contacts] test_082_portal_profile_stats_contacts_count → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_083_portal_profile_stats_sos_count → PASSED in 0.02s</t>
+          <t>[User Portal - Home &amp; SOS] test_083_portal_profile_stats_sos_count → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4668,14 +4668,14 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_084_portal_profile_details_section → PASSED in 0.02s</t>
+          <t>[User Profile] test_084_portal_profile_details_section → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:44</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:09</t>
+          <t>2026-06-16 06:20:45</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4702,14 +4702,14 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>[User Profile] test_086_portal_profile_logout_btn_exists → PASSED in 0.02s</t>
+          <t>[User Profile] test_086_portal_profile_logout_btn_exists → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_089_admin_dashboard_subtitle → PASSED in 0.03s</t>
+          <t>[Admin Command Center] test_089_admin_dashboard_subtitle → PASSED in 0.02s</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4794,7 +4794,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>[Trusted Contacts] test_096_admin_dashboard_stat_card_total_contacts → PASSED in 0.02s</t>
+          <t>[Trusted Contacts] test_096_admin_dashboard_stat_card_total_contacts → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_097_admin_dashboard_hotspots_title → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_097_admin_dashboard_hotspots_title → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4913,7 +4913,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:47</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_101_admin_dashboard_reports_table_title → PASSED in 0.02s</t>
+          <t>[Report Incident] test_101_admin_dashboard_reports_table_title → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:48</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4974,14 +4974,14 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>[Report Incident] test_102_admin_dashboard_reports_table_headers → PASSED in 0.07s</t>
+          <t>[Report Incident] test_102_admin_dashboard_reports_table_headers → PASSED in 0.06s</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:48</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4998,7 +4998,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:48</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -5008,14 +5008,14 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_104_admin_dashboard_users_table_title → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_104_admin_dashboard_users_table_title → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:48</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_105_admin_dashboard_users_table_data → PASSED in 0.02s</t>
+          <t>[Admin Command Center] test_105_admin_dashboard_users_table_data → PASSED in 0.01s</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:48</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:12</t>
+          <t>2026-06-16 06:20:48</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:13</t>
+          <t>2026-06-16 06:20:49</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -5076,14 +5076,14 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_108_admin_dashboard_emergency_modal_details_flow → PASSED in 1.15s</t>
+          <t>[Admin Command Center] test_108_admin_dashboard_emergency_modal_details_flow → PASSED in 1.14s</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:25</t>
+          <t>2026-06-16 06:21:01</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>[User Portal - Home &amp; SOS] test_109_admin_dashboard_resolve_sos_flow → PASSED in 12.18s</t>
+          <t>[User Portal - Home &amp; SOS] test_109_admin_dashboard_resolve_sos_flow → PASSED in 12.15s</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:27</t>
+          <t>2026-06-16 06:21:02</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -5110,14 +5110,14 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>[Admin Command Center] test_110_admin_logout_redirection → PASSED in 1.08s</t>
+          <t>[Admin Command Center] test_110_admin_logout_redirection → PASSED in 1.07s</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16 06:04:27</t>
+          <t>2026-06-16 06:21:02</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>16</v>
+        <v>15.72</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T07:52:35.134081Z</t>
+          <t>2026-06-18T08:11:21.005306Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T07:52:51.130991Z</t>
+          <t>2026-06-18T08:11:36.720838Z</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6110,7 +6110,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6127,7 +6127,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -6144,7 +6144,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6161,7 +6161,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -6178,7 +6178,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6212,7 +6212,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6263,7 +6263,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6280,7 +6280,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6297,7 +6297,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6314,7 +6314,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -6365,7 +6365,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6382,7 +6382,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6450,7 +6450,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6484,7 +6484,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6501,7 +6501,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6535,7 +6535,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6552,7 +6552,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6569,7 +6569,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6586,7 +6586,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6620,7 +6620,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -6637,7 +6637,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6654,7 +6654,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6688,7 +6688,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -6705,7 +6705,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -6739,7 +6739,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6756,7 +6756,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -6773,7 +6773,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6790,7 +6790,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -6807,7 +6807,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6824,7 +6824,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -6875,7 +6875,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6892,7 +6892,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -6909,7 +6909,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -6926,7 +6926,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -6960,7 +6960,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -6994,7 +6994,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -7011,7 +7011,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7062,7 +7062,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -7079,7 +7079,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -7147,7 +7147,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -7181,7 +7181,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7198,7 +7198,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -7232,7 +7232,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -7266,7 +7266,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -7300,7 +7300,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7317,7 +7317,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -7334,7 +7334,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -7402,7 +7402,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7453,7 +7453,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -7470,7 +7470,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7487,7 +7487,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -7572,7 +7572,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -7589,7 +7589,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -7657,7 +7657,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -7691,7 +7691,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7759,7 +7759,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -7776,7 +7776,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -7861,7 +7861,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -7878,7 +7878,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7895,7 +7895,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7912,7 +7912,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7929,7 +7929,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -7946,7 +7946,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -7963,7 +7963,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -8014,7 +8014,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -8031,7 +8031,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -8048,7 +8048,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -8082,7 +8082,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -8099,7 +8099,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -8116,7 +8116,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -8150,7 +8150,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -8184,7 +8184,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -8218,7 +8218,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -8252,7 +8252,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -8269,7 +8269,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -8286,7 +8286,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -8320,7 +8320,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -8388,7 +8388,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -8405,7 +8405,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -8439,7 +8439,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -8456,7 +8456,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -8473,7 +8473,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -8490,7 +8490,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -8507,7 +8507,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -8524,7 +8524,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -8575,7 +8575,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -8609,7 +8609,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -8626,7 +8626,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -8643,7 +8643,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -8660,7 +8660,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -8677,7 +8677,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -8694,7 +8694,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -8728,7 +8728,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -8745,7 +8745,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -8762,7 +8762,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -8779,7 +8779,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -8796,7 +8796,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -8830,7 +8830,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -8847,7 +8847,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -8881,7 +8881,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -8898,7 +8898,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -8915,7 +8915,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -8932,7 +8932,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -8949,7 +8949,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -8983,7 +8983,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -9000,7 +9000,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -9034,7 +9034,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -9068,7 +9068,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -9102,7 +9102,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:50</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -9136,7 +9136,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -9153,7 +9153,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -9170,7 +9170,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -9187,7 +9187,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -9204,7 +9204,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -9221,7 +9221,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -9238,7 +9238,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -9289,7 +9289,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -9306,7 +9306,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -9323,7 +9323,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -9340,7 +9340,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -9357,7 +9357,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -9374,7 +9374,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -9391,7 +9391,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -9408,7 +9408,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -9425,7 +9425,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -9442,7 +9442,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -9459,7 +9459,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -9476,7 +9476,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -9493,7 +9493,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -9510,7 +9510,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -9527,7 +9527,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -9544,7 +9544,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -9561,7 +9561,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -9578,7 +9578,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -9595,7 +9595,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -9612,7 +9612,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -9629,7 +9629,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -9646,7 +9646,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -9663,7 +9663,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -9680,7 +9680,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -9697,7 +9697,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -9714,7 +9714,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -9731,7 +9731,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -9765,7 +9765,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -9782,7 +9782,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -9799,7 +9799,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -9833,7 +9833,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -9850,7 +9850,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -9867,7 +9867,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -9884,7 +9884,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -9901,7 +9901,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -9918,7 +9918,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -9935,7 +9935,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -10003,7 +10003,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -10020,7 +10020,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -10037,7 +10037,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 07:52:51</t>
+          <t>2026-06-18 08:11:36</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.72</v>
+        <v>15.48</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T08:11:21.005306Z</t>
+          <t>2026-06-18T08:24:45.964706Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T08:11:36.720838Z</t>
+          <t>2026-06-18T08:25:01.443826Z</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6110,7 +6110,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6127,7 +6127,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -6144,7 +6144,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6161,7 +6161,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -6178,7 +6178,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6212,7 +6212,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6263,7 +6263,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6280,7 +6280,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6297,7 +6297,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6314,7 +6314,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -6365,7 +6365,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6382,7 +6382,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6450,7 +6450,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6484,7 +6484,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6501,7 +6501,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6535,7 +6535,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6552,7 +6552,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6569,7 +6569,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6586,7 +6586,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6620,7 +6620,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -6637,7 +6637,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6654,7 +6654,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6688,7 +6688,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -6705,7 +6705,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -6739,7 +6739,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6756,7 +6756,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -6773,7 +6773,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6790,7 +6790,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -6807,7 +6807,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6824,7 +6824,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -6875,7 +6875,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6892,7 +6892,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -6909,7 +6909,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -6926,7 +6926,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -6960,7 +6960,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -6994,7 +6994,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -7011,7 +7011,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7062,7 +7062,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -7079,7 +7079,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -7147,7 +7147,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -7181,7 +7181,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7198,7 +7198,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -7232,7 +7232,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -7266,7 +7266,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -7300,7 +7300,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7317,7 +7317,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -7334,7 +7334,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -7402,7 +7402,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7453,7 +7453,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -7470,7 +7470,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7487,7 +7487,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -7572,7 +7572,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -7589,7 +7589,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -7657,7 +7657,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -7691,7 +7691,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7759,7 +7759,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -7776,7 +7776,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -7861,7 +7861,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -7878,7 +7878,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7895,7 +7895,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7912,7 +7912,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7929,7 +7929,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -7946,7 +7946,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -7963,7 +7963,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -8014,7 +8014,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -8031,7 +8031,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -8048,7 +8048,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -8082,7 +8082,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -8099,7 +8099,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -8116,7 +8116,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -8150,7 +8150,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -8184,7 +8184,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -8218,7 +8218,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -8252,7 +8252,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -8269,7 +8269,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -8286,7 +8286,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -8320,7 +8320,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -8388,7 +8388,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -8405,7 +8405,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -8439,7 +8439,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -8456,7 +8456,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -8473,7 +8473,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -8490,7 +8490,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -8507,7 +8507,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -8524,7 +8524,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -8575,7 +8575,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -8609,7 +8609,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -8626,7 +8626,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -8643,7 +8643,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -8660,7 +8660,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -8677,7 +8677,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -8694,7 +8694,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -8728,7 +8728,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -8745,7 +8745,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -8762,7 +8762,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -8779,7 +8779,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -8796,7 +8796,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -8830,7 +8830,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -8847,7 +8847,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -8881,7 +8881,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -8898,7 +8898,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -8915,7 +8915,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -8932,7 +8932,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -8949,7 +8949,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -8983,7 +8983,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -9000,7 +9000,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -9034,7 +9034,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -9068,7 +9068,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -9102,7 +9102,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -9136,7 +9136,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -9153,7 +9153,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -9170,7 +9170,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -9187,7 +9187,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -9204,7 +9204,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -9221,7 +9221,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -9238,7 +9238,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -9289,7 +9289,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -9306,7 +9306,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -9323,7 +9323,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -9340,7 +9340,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -9357,7 +9357,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -9374,7 +9374,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -9391,7 +9391,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -9408,7 +9408,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -9425,7 +9425,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -9442,7 +9442,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -9459,7 +9459,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -9476,7 +9476,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -9493,7 +9493,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -9510,7 +9510,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -9527,7 +9527,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -9544,7 +9544,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -9561,7 +9561,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -9578,7 +9578,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -9595,7 +9595,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -9612,7 +9612,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -9629,7 +9629,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -9646,7 +9646,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -9663,7 +9663,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -9680,7 +9680,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -9697,7 +9697,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -9714,7 +9714,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -9731,7 +9731,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -9765,7 +9765,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -9782,7 +9782,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -9799,7 +9799,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -9833,7 +9833,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -9850,7 +9850,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -9867,7 +9867,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -9884,7 +9884,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -9901,7 +9901,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -9918,7 +9918,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -9935,7 +9935,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -10003,7 +10003,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -10020,7 +10020,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -10037,7 +10037,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:11:36</t>
+          <t>2026-06-18 08:25:01</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.48</v>
+        <v>15.6</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T08:24:45.964706Z</t>
+          <t>2026-06-18T08:38:25.937762Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-18T08:25:01.443826Z</t>
+          <t>2026-06-18T08:38:41.541752Z</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -6110,7 +6110,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6127,7 +6127,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -6144,7 +6144,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -6161,7 +6161,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -6178,7 +6178,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -6195,7 +6195,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -6212,7 +6212,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -6229,7 +6229,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -6263,7 +6263,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6280,7 +6280,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -6297,7 +6297,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -6314,7 +6314,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -6365,7 +6365,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -6382,7 +6382,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -6433,7 +6433,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -6450,7 +6450,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -6484,7 +6484,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6501,7 +6501,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6518,7 +6518,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6535,7 +6535,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6552,7 +6552,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6569,7 +6569,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6586,7 +6586,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -6620,7 +6620,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -6637,7 +6637,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -6654,7 +6654,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -6688,7 +6688,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -6705,7 +6705,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -6722,7 +6722,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -6739,7 +6739,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -6756,7 +6756,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -6773,7 +6773,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -6790,7 +6790,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -6807,7 +6807,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -6824,7 +6824,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -6875,7 +6875,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -6892,7 +6892,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -6909,7 +6909,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -6926,7 +6926,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -6960,7 +6960,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -6994,7 +6994,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -7011,7 +7011,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -7062,7 +7062,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -7079,7 +7079,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -7113,7 +7113,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -7147,7 +7147,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -7181,7 +7181,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -7198,7 +7198,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -7215,7 +7215,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -7232,7 +7232,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -7249,7 +7249,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -7266,7 +7266,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -7300,7 +7300,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -7317,7 +7317,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -7334,7 +7334,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -7402,7 +7402,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -7453,7 +7453,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -7470,7 +7470,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -7487,7 +7487,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -7572,7 +7572,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -7589,7 +7589,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -7657,7 +7657,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -7691,7 +7691,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -7725,7 +7725,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -7759,7 +7759,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -7776,7 +7776,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -7861,7 +7861,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -7878,7 +7878,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -7895,7 +7895,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -7912,7 +7912,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -7929,7 +7929,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -7946,7 +7946,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -7963,7 +7963,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -8014,7 +8014,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -8031,7 +8031,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -8048,7 +8048,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -8082,7 +8082,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -8099,7 +8099,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -8116,7 +8116,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -8133,7 +8133,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -8150,7 +8150,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -8184,7 +8184,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -8218,7 +8218,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -8235,7 +8235,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -8252,7 +8252,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -8269,7 +8269,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -8286,7 +8286,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -8303,7 +8303,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -8320,7 +8320,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -8388,7 +8388,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -8405,7 +8405,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -8422,7 +8422,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -8439,7 +8439,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -8456,7 +8456,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -8473,7 +8473,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -8490,7 +8490,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -8507,7 +8507,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -8524,7 +8524,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -8575,7 +8575,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -8592,7 +8592,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -8609,7 +8609,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -8626,7 +8626,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -8643,7 +8643,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -8660,7 +8660,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -8677,7 +8677,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -8694,7 +8694,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -8728,7 +8728,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -8745,7 +8745,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -8762,7 +8762,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -8779,7 +8779,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -8796,7 +8796,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -8830,7 +8830,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -8847,7 +8847,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -8881,7 +8881,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -8898,7 +8898,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -8915,7 +8915,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -8932,7 +8932,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -8949,7 +8949,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -8966,7 +8966,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -8983,7 +8983,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -9000,7 +9000,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -9017,7 +9017,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -9034,7 +9034,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -9051,7 +9051,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -9068,7 +9068,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -9102,7 +9102,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -9119,7 +9119,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -9136,7 +9136,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -9153,7 +9153,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -9170,7 +9170,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -9187,7 +9187,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -9204,7 +9204,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -9221,7 +9221,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -9238,7 +9238,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -9289,7 +9289,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -9306,7 +9306,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -9323,7 +9323,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -9340,7 +9340,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -9357,7 +9357,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -9374,7 +9374,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -9391,7 +9391,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -9408,7 +9408,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -9425,7 +9425,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -9442,7 +9442,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -9459,7 +9459,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -9476,7 +9476,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -9493,7 +9493,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -9510,7 +9510,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -9527,7 +9527,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -9544,7 +9544,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -9561,7 +9561,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -9578,7 +9578,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -9595,7 +9595,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -9612,7 +9612,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -9629,7 +9629,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -9646,7 +9646,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -9663,7 +9663,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -9680,7 +9680,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -9697,7 +9697,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -9714,7 +9714,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -9731,7 +9731,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -9765,7 +9765,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -9782,7 +9782,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -9799,7 +9799,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -9816,7 +9816,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -9833,7 +9833,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -9850,7 +9850,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -9867,7 +9867,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -9884,7 +9884,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -9901,7 +9901,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -9918,7 +9918,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -9935,7 +9935,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -9952,7 +9952,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -10003,7 +10003,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -10020,7 +10020,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -10037,7 +10037,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18 08:25:01</t>
+          <t>2026-06-18 08:38:41</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13.76</v>
+        <v>15.55</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T05:23:04.347237Z</t>
+          <t>2026-06-22T05:44:10.720580Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T05:23:18.104602Z</t>
+          <t>2026-06-22T05:44:26.272599Z</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -8359,7 +8359,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8563,7 +8563,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -8614,7 +8614,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -8682,7 +8682,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -8716,7 +8716,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -8767,7 +8767,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -8920,7 +8920,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8954,7 +8954,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -9090,7 +9090,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -9107,7 +9107,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -9124,7 +9124,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9141,7 +9141,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -9260,7 +9260,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9277,7 +9277,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9311,7 +9311,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -9362,7 +9362,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9413,7 +9413,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9498,7 +9498,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9583,7 +9583,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -9600,7 +9600,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -9668,7 +9668,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -9702,7 +9702,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -9770,7 +9770,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -9787,7 +9787,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -9821,7 +9821,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -9838,7 +9838,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9855,7 +9855,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -9872,7 +9872,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9889,7 +9889,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9940,7 +9940,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9957,7 +9957,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10008,7 +10008,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10093,7 +10093,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10127,7 +10127,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10161,7 +10161,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10178,7 +10178,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10212,7 +10212,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -10263,7 +10263,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10297,7 +10297,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10331,7 +10331,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10365,7 +10365,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10382,7 +10382,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -10399,7 +10399,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10416,7 +10416,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10484,7 +10484,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -10637,7 +10637,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -10705,7 +10705,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -10722,7 +10722,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -10739,7 +10739,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -10756,7 +10756,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -10773,7 +10773,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -10824,7 +10824,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -10858,7 +10858,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -10875,7 +10875,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -10926,7 +10926,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -10943,7 +10943,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -11028,7 +11028,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -11062,7 +11062,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -11130,7 +11130,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -11164,7 +11164,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -11266,7 +11266,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -11283,7 +11283,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -11300,7 +11300,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -11351,7 +11351,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -11402,7 +11402,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -11419,7 +11419,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -11453,7 +11453,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -11470,7 +11470,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -11487,7 +11487,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -11674,7 +11674,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -11691,7 +11691,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -11776,7 +11776,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -11861,7 +11861,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -11946,7 +11946,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -11997,7 +11997,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -12031,7 +12031,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -12133,7 +12133,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -12167,7 +12167,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -12201,7 +12201,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -12286,7 +12286,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -12320,7 +12320,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -12337,7 +12337,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -12354,7 +12354,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -12388,7 +12388,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -12439,7 +12439,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -12473,7 +12473,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -12490,7 +12490,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:17</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -12677,7 +12677,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:23:18</t>
+          <t>2026-06-22 05:44:26</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.55</v>
+        <v>15.5</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T05:44:10.720580Z</t>
+          <t>2026-06-22T06:18:19.102187Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T05:44:26.272599Z</t>
+          <t>2026-06-22T06:18:34.598780Z</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -8359,7 +8359,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8563,7 +8563,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -8614,7 +8614,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -8682,7 +8682,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -8716,7 +8716,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -8767,7 +8767,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -8920,7 +8920,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8954,7 +8954,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -9090,7 +9090,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -9107,7 +9107,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -9124,7 +9124,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9141,7 +9141,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -9260,7 +9260,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9277,7 +9277,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9311,7 +9311,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -9362,7 +9362,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9413,7 +9413,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9498,7 +9498,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9583,7 +9583,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -9600,7 +9600,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -9668,7 +9668,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -9702,7 +9702,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -9770,7 +9770,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -9787,7 +9787,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -9821,7 +9821,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -9838,7 +9838,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9855,7 +9855,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -9872,7 +9872,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9889,7 +9889,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9940,7 +9940,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9957,7 +9957,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10008,7 +10008,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10093,7 +10093,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10127,7 +10127,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10161,7 +10161,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10178,7 +10178,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10212,7 +10212,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -10263,7 +10263,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10297,7 +10297,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10331,7 +10331,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10365,7 +10365,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10382,7 +10382,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -10399,7 +10399,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10416,7 +10416,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10484,7 +10484,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -10637,7 +10637,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -10705,7 +10705,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -10722,7 +10722,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -10739,7 +10739,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -10756,7 +10756,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -10773,7 +10773,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -10824,7 +10824,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -10858,7 +10858,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -10875,7 +10875,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -10926,7 +10926,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -10943,7 +10943,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -11028,7 +11028,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -11062,7 +11062,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -11130,7 +11130,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -11164,7 +11164,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -11266,7 +11266,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -11283,7 +11283,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -11300,7 +11300,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -11351,7 +11351,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -11402,7 +11402,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -11419,7 +11419,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -11453,7 +11453,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -11470,7 +11470,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -11487,7 +11487,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -11674,7 +11674,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -11691,7 +11691,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -11776,7 +11776,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -11861,7 +11861,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -11946,7 +11946,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -11997,7 +11997,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -12031,7 +12031,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -12133,7 +12133,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -12167,7 +12167,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -12201,7 +12201,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -12286,7 +12286,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -12320,7 +12320,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -12337,7 +12337,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -12354,7 +12354,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -12388,7 +12388,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -12439,7 +12439,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -12473,7 +12473,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -12490,7 +12490,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -12677,7 +12677,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:44:26</t>
+          <t>2026-06-22 06:18:34</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.5</v>
+        <v>15.68</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T06:18:19.102187Z</t>
+          <t>2026-06-22T06:24:27.784212Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T06:18:34.598780Z</t>
+          <t>2026-06-22T06:24:43.464129Z</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -8359,7 +8359,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8563,7 +8563,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -8614,7 +8614,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -8682,7 +8682,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -8716,7 +8716,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -8767,7 +8767,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -8920,7 +8920,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8954,7 +8954,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -9090,7 +9090,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -9107,7 +9107,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -9124,7 +9124,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9141,7 +9141,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -9260,7 +9260,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9277,7 +9277,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9311,7 +9311,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -9362,7 +9362,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9413,7 +9413,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9498,7 +9498,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9583,7 +9583,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -9600,7 +9600,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -9668,7 +9668,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -9702,7 +9702,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -9770,7 +9770,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -9787,7 +9787,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -9821,7 +9821,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -9838,7 +9838,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9855,7 +9855,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -9872,7 +9872,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9889,7 +9889,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9940,7 +9940,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9957,7 +9957,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10008,7 +10008,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10093,7 +10093,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10127,7 +10127,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10161,7 +10161,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10178,7 +10178,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10212,7 +10212,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -10263,7 +10263,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10297,7 +10297,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10331,7 +10331,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10365,7 +10365,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10382,7 +10382,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -10399,7 +10399,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10416,7 +10416,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10484,7 +10484,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -10637,7 +10637,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -10705,7 +10705,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -10722,7 +10722,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -10739,7 +10739,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -10756,7 +10756,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -10773,7 +10773,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -10824,7 +10824,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -10858,7 +10858,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -10875,7 +10875,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -10926,7 +10926,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -10943,7 +10943,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -11028,7 +11028,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -11062,7 +11062,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -11130,7 +11130,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -11164,7 +11164,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -11266,7 +11266,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -11283,7 +11283,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -11300,7 +11300,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -11351,7 +11351,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -11402,7 +11402,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -11419,7 +11419,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -11453,7 +11453,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -11470,7 +11470,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -11487,7 +11487,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -11674,7 +11674,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -11691,7 +11691,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -11776,7 +11776,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -11861,7 +11861,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -11946,7 +11946,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -11997,7 +11997,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -12031,7 +12031,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -12133,7 +12133,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -12167,7 +12167,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -12201,7 +12201,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -12286,7 +12286,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -12320,7 +12320,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -12337,7 +12337,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -12354,7 +12354,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -12388,7 +12388,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -12439,7 +12439,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -12473,7 +12473,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -12490,7 +12490,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -12677,7 +12677,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:18:34</t>
+          <t>2026-06-22 06:24:43</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.68</v>
+        <v>15.5</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T06:24:27.784212Z</t>
+          <t>2026-06-23T06:08:06.104343Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T06:24:43.464129Z</t>
+          <t>2026-06-23T06:08:21.607564Z</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -8359,7 +8359,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8563,7 +8563,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -8614,7 +8614,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -8682,7 +8682,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -8716,7 +8716,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -8767,7 +8767,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -8920,7 +8920,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8954,7 +8954,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -9090,7 +9090,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -9107,7 +9107,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -9124,7 +9124,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9141,7 +9141,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -9260,7 +9260,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9277,7 +9277,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9311,7 +9311,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -9362,7 +9362,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9413,7 +9413,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9498,7 +9498,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9583,7 +9583,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -9600,7 +9600,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -9668,7 +9668,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -9702,7 +9702,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -9770,7 +9770,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -9787,7 +9787,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -9821,7 +9821,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -9838,7 +9838,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9855,7 +9855,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -9872,7 +9872,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9889,7 +9889,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9940,7 +9940,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9957,7 +9957,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10008,7 +10008,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10093,7 +10093,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10127,7 +10127,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10161,7 +10161,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10178,7 +10178,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10212,7 +10212,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -10263,7 +10263,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10297,7 +10297,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10331,7 +10331,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10365,7 +10365,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10382,7 +10382,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -10399,7 +10399,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10416,7 +10416,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10484,7 +10484,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -10637,7 +10637,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -10705,7 +10705,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -10722,7 +10722,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -10739,7 +10739,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -10756,7 +10756,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -10773,7 +10773,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -10824,7 +10824,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -10858,7 +10858,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -10875,7 +10875,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -10926,7 +10926,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -10943,7 +10943,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -11028,7 +11028,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -11062,7 +11062,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -11130,7 +11130,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -11164,7 +11164,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -11266,7 +11266,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -11283,7 +11283,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -11300,7 +11300,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -11351,7 +11351,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -11402,7 +11402,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -11419,7 +11419,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -11453,7 +11453,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -11470,7 +11470,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -11487,7 +11487,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -11674,7 +11674,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -11691,7 +11691,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -11776,7 +11776,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -11861,7 +11861,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -11946,7 +11946,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -11997,7 +11997,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -12031,7 +12031,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -12133,7 +12133,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -12167,7 +12167,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -12201,7 +12201,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -12286,7 +12286,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -12320,7 +12320,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -12337,7 +12337,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -12354,7 +12354,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -12388,7 +12388,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -12439,7 +12439,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -12473,7 +12473,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -12490,7 +12490,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -12677,7 +12677,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22 06:24:43</t>
+          <t>2026-06-23 06:08:21</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T06:08:06.104343Z</t>
+          <t>2026-06-23T07:09:26.985841Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T06:08:21.607564Z</t>
+          <t>2026-06-23T07:09:42.687845Z</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -8359,7 +8359,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8563,7 +8563,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -8614,7 +8614,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -8682,7 +8682,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -8716,7 +8716,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -8767,7 +8767,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -8920,7 +8920,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8954,7 +8954,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -9090,7 +9090,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -9107,7 +9107,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -9124,7 +9124,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9141,7 +9141,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -9260,7 +9260,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9277,7 +9277,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9311,7 +9311,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -9362,7 +9362,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9413,7 +9413,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9498,7 +9498,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9583,7 +9583,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -9600,7 +9600,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -9668,7 +9668,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -9702,7 +9702,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -9770,7 +9770,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -9787,7 +9787,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -9821,7 +9821,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -9838,7 +9838,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9855,7 +9855,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -9872,7 +9872,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9889,7 +9889,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9940,7 +9940,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9957,7 +9957,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10008,7 +10008,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10093,7 +10093,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10127,7 +10127,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10161,7 +10161,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10178,7 +10178,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10212,7 +10212,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -10263,7 +10263,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10297,7 +10297,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10331,7 +10331,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10365,7 +10365,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10382,7 +10382,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -10399,7 +10399,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10416,7 +10416,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10484,7 +10484,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -10637,7 +10637,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -10705,7 +10705,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -10722,7 +10722,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -10739,7 +10739,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -10756,7 +10756,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -10773,7 +10773,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -10824,7 +10824,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -10858,7 +10858,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -10875,7 +10875,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -10926,7 +10926,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -10943,7 +10943,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -11028,7 +11028,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -11062,7 +11062,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -11130,7 +11130,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -11164,7 +11164,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -11266,7 +11266,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -11283,7 +11283,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -11300,7 +11300,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -11351,7 +11351,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -11402,7 +11402,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -11419,7 +11419,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -11453,7 +11453,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -11470,7 +11470,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -11487,7 +11487,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -11674,7 +11674,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -11691,7 +11691,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -11776,7 +11776,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -11861,7 +11861,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -11946,7 +11946,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -11997,7 +11997,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -12031,7 +12031,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -12133,7 +12133,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -12167,7 +12167,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -12201,7 +12201,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -12286,7 +12286,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -12320,7 +12320,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -12337,7 +12337,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -12354,7 +12354,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -12388,7 +12388,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -12439,7 +12439,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -12473,7 +12473,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -12490,7 +12490,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -12677,7 +12677,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 06:08:21</t>
+          <t>2026-06-23 07:09:42</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">

--- a/sentinel-web/E2E_Test_Report_Sentinel.xlsx
+++ b/sentinel-web/E2E_Test_Report_Sentinel.xlsx
@@ -540,16 +540,16 @@
         <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15.7</v>
+        <v>15.63</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T07:09:26.985841Z</t>
+          <t>2026-06-23T07:22:46.749982Z</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23T07:09:42.687845Z</t>
+          <t>2026-06-23T07:23:02.378178Z</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7798,7 +7798,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -7832,7 +7832,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -7883,7 +7883,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -7968,7 +7968,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -8002,7 +8002,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8070,7 +8070,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -8087,7 +8087,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8257,7 +8257,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -8359,7 +8359,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -8427,7 +8427,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -8444,7 +8444,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -8461,7 +8461,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -8478,7 +8478,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -8512,7 +8512,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -8529,7 +8529,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8563,7 +8563,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -8614,7 +8614,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -8665,7 +8665,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -8682,7 +8682,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -8716,7 +8716,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -8733,7 +8733,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -8767,7 +8767,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -8801,7 +8801,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -8818,7 +8818,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -8886,7 +8886,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -8920,7 +8920,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -8937,7 +8937,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -8954,7 +8954,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -8988,7 +8988,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -9022,7 +9022,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -9056,7 +9056,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -9090,7 +9090,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -9107,7 +9107,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -9124,7 +9124,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -9141,7 +9141,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -9175,7 +9175,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -9243,7 +9243,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -9260,7 +9260,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -9277,7 +9277,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -9294,7 +9294,7 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -9311,7 +9311,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -9328,7 +9328,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -9362,7 +9362,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -9413,7 +9413,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -9430,7 +9430,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -9464,7 +9464,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -9481,7 +9481,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -9498,7 +9498,7 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -9532,7 +9532,7 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -9583,7 +9583,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -9600,7 +9600,7 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -9617,7 +9617,7 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -9651,7 +9651,7 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -9668,7 +9668,7 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -9685,7 +9685,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -9702,7 +9702,7 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -9736,7 +9736,7 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -9770,7 +9770,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -9787,7 +9787,7 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -9821,7 +9821,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -9838,7 +9838,7 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -9855,7 +9855,7 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -9872,7 +9872,7 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -9889,7 +9889,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -9923,7 +9923,7 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -9940,7 +9940,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -9957,7 +9957,7 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -9974,7 +9974,7 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -10008,7 +10008,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -10025,7 +10025,7 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -10093,7 +10093,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -10110,7 +10110,7 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -10127,7 +10127,7 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -10144,7 +10144,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -10161,7 +10161,7 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -10178,7 +10178,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -10212,7 +10212,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -10263,7 +10263,7 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -10297,7 +10297,7 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -10314,7 +10314,7 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -10331,7 +10331,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -10365,7 +10365,7 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -10382,7 +10382,7 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -10399,7 +10399,7 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -10416,7 +10416,7 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -10450,7 +10450,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -10484,7 +10484,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -10501,7 +10501,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -10518,7 +10518,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -10535,7 +10535,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -10552,7 +10552,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -10569,7 +10569,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -10603,7 +10603,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -10620,7 +10620,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -10637,7 +10637,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -10654,7 +10654,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -10705,7 +10705,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -10722,7 +10722,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -10739,7 +10739,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -10756,7 +10756,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -10773,7 +10773,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -10807,7 +10807,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -10824,7 +10824,7 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -10858,7 +10858,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -10875,7 +10875,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -10909,7 +10909,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -10926,7 +10926,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -10943,7 +10943,7 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -10960,7 +10960,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -11011,7 +11011,7 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -11028,7 +11028,7 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -11062,7 +11062,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -11096,7 +11096,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -11113,7 +11113,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -11130,7 +11130,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -11164,7 +11164,7 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -11181,7 +11181,7 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -11198,7 +11198,7 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -11215,7 +11215,7 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -11232,7 +11232,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -11266,7 +11266,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -11283,7 +11283,7 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -11300,7 +11300,7 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -11317,7 +11317,7 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -11334,7 +11334,7 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -11351,7 +11351,7 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -11385,7 +11385,7 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -11402,7 +11402,7 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -11419,7 +11419,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -11436,7 +11436,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -11453,7 +11453,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -11470,7 +11470,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -11487,7 +11487,7 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -11538,7 +11538,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -11555,7 +11555,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -11572,7 +11572,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -11640,7 +11640,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -11674,7 +11674,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -11691,7 +11691,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -11725,7 +11725,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -11742,7 +11742,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -11776,7 +11776,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -11793,7 +11793,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -11810,7 +11810,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -11827,7 +11827,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -11861,7 +11861,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
@@ -11878,7 +11878,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -11895,7 +11895,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -11929,7 +11929,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
@@ -11946,7 +11946,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -11963,7 +11963,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
@@ -11980,7 +11980,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -11997,7 +11997,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
@@ -12014,7 +12014,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -12031,7 +12031,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B263" s="3" t="inlineStr">
@@ -12048,7 +12048,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr">
@@ -12082,7 +12082,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -12099,7 +12099,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr">
@@ -12116,7 +12116,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -12133,7 +12133,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -12167,7 +12167,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -12201,7 +12201,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -12235,7 +12235,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr">
@@ -12252,7 +12252,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr">
@@ -12286,7 +12286,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -12303,7 +12303,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr">
@@ -12320,7 +12320,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -12337,7 +12337,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr">
@@ -12354,7 +12354,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr">
@@ -12388,7 +12388,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -12439,7 +12439,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr">
@@ -12456,7 +12456,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -12473,7 +12473,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr">
@@ -12490,7 +12490,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B291" s="3" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -12541,7 +12541,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B293" s="3" t="inlineStr">
@@ -12558,7 +12558,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B295" s="3" t="inlineStr">
@@ -12592,7 +12592,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -12609,7 +12609,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B297" s="3" t="inlineStr">
@@ -12626,7 +12626,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B299" s="3" t="inlineStr">
@@ -12660,7 +12660,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -12677,7 +12677,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23 07:09:42</t>
+          <t>2026-06-23 07:23:02</t>
         </is>
       </c>
       <c r="B301" s="3" t="inlineStr">
